--- a/LocalizationTest.xlsx
+++ b/LocalizationTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jerry/Projects/GitHub/UniSharper.Localization/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/External/Projects/GitHub/UniSharper.Localization/master/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565A812D-7775-C24A-B1FC-659ACDBE6C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30166B57-4943-0146-AE8D-B309FE7B4959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="800" yWindow="960" windowWidth="35580" windowHeight="18300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,18 +98,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I Love You!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我爱你！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我愛妳！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>你好</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -145,56 +133,70 @@
     <t>¡Adiós!</t>
   </si>
   <si>
-    <t>¡Te quiero!</t>
+    <t>¡Gracias!</t>
+  </si>
+  <si>
+    <t>es</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>es.Style</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TranslationKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(font:LiberationSans SDF, fontSize:36, fontMaterial:LiberationSans SDF Material, colorGradientPreset:Yellow to Orange - Vertical)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(font:LiberationSans SDF, fontSize:42, fontMaterial:LiberationSans SDF Material, colorGradientPreset:Yellow to Orange - Vertical)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(font:Tanks SDF, fontSize:36, fontMaterial:Tanks Atlas Material, colorGradientPreset:Light to Dark Green - Vertical)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(font:Tanks SDF, fontSize:42, fontMaterial:Tanks Atlas Material, colorGradientPreset:Light to Dark Green - Vertical)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(font:Tanks SDF, fontSize:36, fontMaterial:Tanks Atlas Material, colorGradientPreset:Dark to Light Green - Vertical)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(font:Tanks SDF, fontSize:42, fontMaterial:Tanks Atlas Material, colorGradientPreset:Dark to Light Green - Vertical)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(font:LiberationSans SDF, fontSize:36, fontMaterial:LiberationSans SDF Material, colorGradientPreset:Blue to Purple - Vertical)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(font:LiberationSans SDF, fontSize:42, fontMaterial:LiberationSans SDF Material, colorGradientPreset:Blue to Purple - Vertical)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>¡Hola!</t>
-  </si>
-  <si>
-    <t>¡Gracias!</t>
-  </si>
-  <si>
-    <t>es</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>es.Style</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TranslationKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(font:LiberationSans SDF, fontSize:36, fontMaterial:LiberationSans SDF Material, colorGradientPreset:Yellow to Orange - Vertical)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(font:LiberationSans SDF, fontSize:42, fontMaterial:LiberationSans SDF Material, colorGradientPreset:Yellow to Orange - Vertical)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(font:Tanks SDF, fontSize:36, fontMaterial:Tanks Atlas Material, colorGradientPreset:Light to Dark Green - Vertical)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(font:Tanks SDF, fontSize:42, fontMaterial:Tanks Atlas Material, colorGradientPreset:Light to Dark Green - Vertical)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(font:Tanks SDF, fontSize:36, fontMaterial:Tanks Atlas Material, colorGradientPreset:Dark to Light Green - Vertical)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(font:Tanks SDF, fontSize:42, fontMaterial:Tanks Atlas Material, colorGradientPreset:Dark to Light Green - Vertical)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(font:LiberationSans SDF, fontSize:36, fontMaterial:LiberationSans SDF Material, colorGradientPreset:Blue to Purple - Vertical)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(font:LiberationSans SDF, fontSize:42, fontMaterial:LiberationSans SDF Material, colorGradientPreset:Blue to Purple - Vertical)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}, I Love You!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}，我爱你！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}，我愛妳！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}, ¡Te quiero!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -578,7 +580,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>13</v>
@@ -587,27 +589,27 @@
         <v>0</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="J1" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -622,24 +624,24 @@
         <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
@@ -654,19 +656,19 @@
         <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +698,7 @@
     <row r="1" spans="1:10">
       <c r="A1" s="1"/>
       <c r="B1" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>13</v>
@@ -705,27 +707,27 @@
         <v>0</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="J1" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -740,51 +742,51 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="22">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
